--- a/entertainment_forms/008_entertainment_tech_consultation_request_form--entertainment_forms.xlsx
+++ b/entertainment_forms/008_entertainment_tech_consultation_request_form--entertainment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -789,8 +789,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -818,12 +818,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -835,12 +835,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -852,12 +852,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_14,_'label':_'video_equipment'}</t>
+          <t>video_equipment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 14, 'label': 'Video Equipment'}</t>
+          <t>Video Equipment</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_15,_'label':_'photography'}</t>
+          <t>photography</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 15, 'label': 'Photography'}</t>
+          <t>Photography</t>
         </is>
       </c>
     </row>
@@ -886,12 +886,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_16,_'label':_'audio'}</t>
+          <t>audio</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 16, 'label': 'Audio'}</t>
+          <t>Audio</t>
         </is>
       </c>
     </row>
